--- a/testakten/kurpfalz-taxware-software-ip-insolvenz/05_Finanzierung_Sicherheiten/03_Anlage_IP_Rechtebestand.xlsx
+++ b/testakten/kurpfalz-taxware-software-ip-insolvenz/05_Finanzierung_Sicherheiten/03_Anlage_IP_Rechtebestand.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S-1_Produkte_Rechte" sheetId="1" r:id="R8d45c74280ba40be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S-2_Repositorien" sheetId="2" r:id="R1e26ade4f88b4810"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S-3_Rechtenachweise" sheetId="3" r:id="R41cdb2aa2968406f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S-1_Produkte_Rechte" sheetId="1" r:id="R070dc186c9404b22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S-2_Repositorien" sheetId="2" r:id="R0f1ebb7d04024b22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S-3_Rechtenachweise" sheetId="3" r:id="R1c28ebd308394d77"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/testakten/kurpfalz-taxware-software-ip-insolvenz/05_Finanzierung_Sicherheiten/03_Anlage_IP_Rechtebestand.xlsx
+++ b/testakten/kurpfalz-taxware-software-ip-insolvenz/05_Finanzierung_Sicherheiten/03_Anlage_IP_Rechtebestand.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S-1_Produkte_Rechte" sheetId="1" r:id="R070dc186c9404b22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S-2_Repositorien" sheetId="2" r:id="R0f1ebb7d04024b22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S-3_Rechtenachweise" sheetId="3" r:id="R1c28ebd308394d77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S-1_Produkte_Rechte" sheetId="1" r:id="Rebc766b1a11c4c0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S-2_Repositorien" sheetId="2" r:id="R3072fb88ec854063"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S-3_Rechtenachweise" sheetId="3" r:id="R869575fe69864d22"/>
   </x:sheets>
 </x:workbook>
 </file>
